--- a/Hyderabad-April-2025.xlsx
+++ b/Hyderabad-April-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="63">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Hyderabad</t>
   </si>
   <si>
@@ -151,13 +154,13 @@
     <t>MH43BP4027</t>
   </si>
   <si>
-    <t>TS09UE 3183</t>
-  </si>
-  <si>
-    <t>TS09UE 3184</t>
-  </si>
-  <si>
-    <t>TS09UE 3198</t>
+    <t>TS09UE3183</t>
+  </si>
+  <si>
+    <t>TS09UE3184</t>
+  </si>
+  <si>
+    <t>TS09UE3198</t>
   </si>
   <si>
     <t>TS09UE3947</t>
@@ -178,7 +181,7 @@
     <t>JAGUAR</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>CAMRY</t>
@@ -187,16 +190,16 @@
     <t>Etios</t>
   </si>
   <si>
-    <t>Bolero</t>
-  </si>
-  <si>
-    <t>Safari</t>
-  </si>
-  <si>
-    <t>BYD</t>
-  </si>
-  <si>
-    <t>Dzire</t>
+    <t>BOLERO</t>
+  </si>
+  <si>
+    <t>SAFARI</t>
+  </si>
+  <si>
+    <t>BYD E6</t>
+  </si>
+  <si>
+    <t>DZIRE</t>
   </si>
   <si>
     <t>-</t>
@@ -206,6 +209,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -258,11 +264,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -557,10 +564,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:AA26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -639,27 +646,30 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G2">
+        <v>54</v>
+      </c>
+      <c r="G2" s="2">
         <v>43372</v>
       </c>
       <c r="H2">
@@ -720,26 +730,26 @@
         <v>81.52</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>85</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3">
+        <v>55</v>
+      </c>
+      <c r="G3" s="2">
         <v>43326</v>
       </c>
       <c r="H3">
@@ -800,27 +810,27 @@
         <v>45.4</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="G4" s="2">
+        <v>43326</v>
       </c>
       <c r="H4">
         <v>155937</v>
@@ -880,27 +890,27 @@
         <v>70.95999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>87</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="G5" s="2">
+        <v>43326</v>
       </c>
       <c r="H5">
         <v>170115</v>
@@ -960,26 +970,26 @@
         <v>51.22</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>88</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6">
+        <v>55</v>
+      </c>
+      <c r="G6" s="2">
         <v>43879</v>
       </c>
       <c r="H6">
@@ -1040,27 +1050,27 @@
         <v>60.16</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>89</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="G7" s="2">
+        <v>43818</v>
       </c>
       <c r="H7">
         <v>306767</v>
@@ -1120,27 +1130,27 @@
         <v>66.31</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>90</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="G8" s="2">
+        <v>43006</v>
       </c>
       <c r="H8">
         <v>217127</v>
@@ -1197,30 +1207,30 @@
         <v>0</v>
       </c>
       <c r="Z8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>91</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="G9" s="2">
+        <v>43138</v>
       </c>
       <c r="H9">
         <v>225752</v>
@@ -1280,27 +1290,27 @@
         <v>60.82</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>92</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="G10" s="2">
+        <v>43160</v>
       </c>
       <c r="H10">
         <v>179765</v>
@@ -1360,26 +1370,26 @@
         <v>60.65</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>93</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
+        <v>55</v>
+      </c>
+      <c r="G11" s="2">
         <v>44866</v>
       </c>
       <c r="H11">
@@ -1440,26 +1450,26 @@
         <v>52.22</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>94</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12">
+        <v>55</v>
+      </c>
+      <c r="G12" s="2">
         <v>44866</v>
       </c>
       <c r="H12">
@@ -1520,26 +1530,26 @@
         <v>55.58</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>95</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13">
+        <v>55</v>
+      </c>
+      <c r="G13" s="2">
         <v>45230</v>
       </c>
       <c r="H13">
@@ -1600,26 +1610,26 @@
         <v>28.77</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>96</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
+        <v>55</v>
+      </c>
+      <c r="G14" s="2">
         <v>45230</v>
       </c>
       <c r="H14">
@@ -1680,26 +1690,26 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
+        <v>55</v>
+      </c>
+      <c r="G15" s="2">
         <v>43825</v>
       </c>
       <c r="H15">
@@ -1760,26 +1770,26 @@
         <v>71.13</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16">
+        <v>56</v>
+      </c>
+      <c r="G16" s="2">
         <v>44712</v>
       </c>
       <c r="H16">
@@ -1845,21 +1855,21 @@
         <v>99</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17">
+        <v>57</v>
+      </c>
+      <c r="G17" s="2">
         <v>43554</v>
       </c>
       <c r="H17">
@@ -1917,7 +1927,7 @@
         <v>-10745</v>
       </c>
       <c r="Z17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:26">
@@ -1925,21 +1935,21 @@
         <v>100</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18">
+        <v>57</v>
+      </c>
+      <c r="G18" s="2">
         <v>43663</v>
       </c>
       <c r="H18">
@@ -2005,22 +2015,22 @@
         <v>101</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" t="s">
-        <v>61</v>
+        <v>58</v>
+      </c>
+      <c r="G19" s="2">
+        <v>45294</v>
       </c>
       <c r="H19">
         <v>85192</v>
@@ -2085,22 +2095,22 @@
         <v>102</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20" t="s">
-        <v>61</v>
+        <v>58</v>
+      </c>
+      <c r="G20" s="2">
+        <v>45294</v>
       </c>
       <c r="H20">
         <v>56990</v>
@@ -2165,22 +2175,22 @@
         <v>103</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21" t="s">
-        <v>61</v>
+        <v>58</v>
+      </c>
+      <c r="G21" s="2">
+        <v>45294</v>
       </c>
       <c r="H21">
         <v>75350</v>
@@ -2245,21 +2255,21 @@
         <v>104</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22">
+        <v>59</v>
+      </c>
+      <c r="G22" s="2">
         <v>45363</v>
       </c>
       <c r="H22">
@@ -2325,21 +2335,21 @@
         <v>105</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23">
+        <v>59</v>
+      </c>
+      <c r="G23" s="2">
         <v>45363</v>
       </c>
       <c r="H23">
@@ -2405,21 +2415,21 @@
         <v>106</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>59</v>
-      </c>
-      <c r="G24">
+        <v>60</v>
+      </c>
+      <c r="G24" s="2">
         <v>45365</v>
       </c>
       <c r="H24">
@@ -2485,21 +2495,21 @@
         <v>107</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25">
+        <v>61</v>
+      </c>
+      <c r="G25" s="2">
         <v>45392</v>
       </c>
       <c r="H25">
@@ -2565,21 +2575,21 @@
         <v>108</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2025</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26">
+        <v>61</v>
+      </c>
+      <c r="G26" s="2">
         <v>45392</v>
       </c>
       <c r="H26">

--- a/Hyderabad-April-2025.xlsx
+++ b/Hyderabad-April-2025.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2023031\Documents\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B51CB4-2F03-4ECB-8191-05EFADF34919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="3240" yWindow="3240" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -187,9 +193,6 @@
     <t>CAMRY</t>
   </si>
   <si>
-    <t>Etios</t>
-  </si>
-  <si>
     <t>BOLERO</t>
   </si>
   <si>
@@ -203,16 +206,19 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>ETIOS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,13 +282,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -320,7 +334,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -354,6 +368,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -388,9 +403,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -563,11 +579,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:27">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -650,7 +666,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:27">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>84</v>
       </c>
@@ -730,7 +746,7 @@
         <v>81.52</v>
       </c>
     </row>
-    <row r="3" spans="1:27">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>85</v>
       </c>
@@ -810,7 +826,7 @@
         <v>45.4</v>
       </c>
     </row>
-    <row r="4" spans="1:27">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>86</v>
       </c>
@@ -887,10 +903,10 @@
         <v>118396</v>
       </c>
       <c r="Z4">
-        <v>70.95999999999999</v>
+        <v>70.959999999999994</v>
       </c>
     </row>
-    <row r="5" spans="1:27">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>87</v>
       </c>
@@ -970,7 +986,7 @@
         <v>51.22</v>
       </c>
     </row>
-    <row r="6" spans="1:27">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>88</v>
       </c>
@@ -1050,7 +1066,7 @@
         <v>60.16</v>
       </c>
     </row>
-    <row r="7" spans="1:27">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>89</v>
       </c>
@@ -1130,7 +1146,7 @@
         <v>66.31</v>
       </c>
     </row>
-    <row r="8" spans="1:27">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>90</v>
       </c>
@@ -1207,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="Z8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:27">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>91</v>
       </c>
@@ -1290,7 +1306,7 @@
         <v>60.82</v>
       </c>
     </row>
-    <row r="10" spans="1:27">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>92</v>
       </c>
@@ -1370,7 +1386,7 @@
         <v>60.65</v>
       </c>
     </row>
-    <row r="11" spans="1:27">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>93</v>
       </c>
@@ -1450,7 +1466,7 @@
         <v>52.22</v>
       </c>
     </row>
-    <row r="12" spans="1:27">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>94</v>
       </c>
@@ -1530,7 +1546,7 @@
         <v>55.58</v>
       </c>
     </row>
-    <row r="13" spans="1:27">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>95</v>
       </c>
@@ -1610,7 +1626,7 @@
         <v>28.77</v>
       </c>
     </row>
-    <row r="14" spans="1:27">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>96</v>
       </c>
@@ -1690,7 +1706,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="15" spans="1:27">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>97</v>
       </c>
@@ -1770,7 +1786,7 @@
         <v>71.13</v>
       </c>
     </row>
-    <row r="16" spans="1:27">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>98</v>
       </c>
@@ -1850,7 +1866,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="17" spans="1:26">
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>99</v>
       </c>
@@ -1867,7 +1883,7 @@
         <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G17" s="2">
         <v>43554</v>
@@ -1927,10 +1943,10 @@
         <v>-10745</v>
       </c>
       <c r="Z17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:26">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>100</v>
       </c>
@@ -1947,7 +1963,7 @@
         <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G18" s="2">
         <v>43663</v>
@@ -2010,7 +2026,7 @@
         <v>75.16</v>
       </c>
     </row>
-    <row r="19" spans="1:26">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>101</v>
       </c>
@@ -2027,7 +2043,7 @@
         <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G19" s="2">
         <v>45294</v>
@@ -2090,7 +2106,7 @@
         <v>24.46</v>
       </c>
     </row>
-    <row r="20" spans="1:26">
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>102</v>
       </c>
@@ -2107,7 +2123,7 @@
         <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G20" s="2">
         <v>45294</v>
@@ -2170,7 +2186,7 @@
         <v>26.69</v>
       </c>
     </row>
-    <row r="21" spans="1:26">
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>103</v>
       </c>
@@ -2187,7 +2203,7 @@
         <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G21" s="2">
         <v>45294</v>
@@ -2250,7 +2266,7 @@
         <v>30.72</v>
       </c>
     </row>
-    <row r="22" spans="1:26">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>104</v>
       </c>
@@ -2267,7 +2283,7 @@
         <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G22" s="2">
         <v>45363</v>
@@ -2330,7 +2346,7 @@
         <v>-23.82</v>
       </c>
     </row>
-    <row r="23" spans="1:26">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>105</v>
       </c>
@@ -2347,7 +2363,7 @@
         <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G23" s="2">
         <v>45363</v>
@@ -2410,7 +2426,7 @@
         <v>-22.6</v>
       </c>
     </row>
-    <row r="24" spans="1:26">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>106</v>
       </c>
@@ -2427,7 +2443,7 @@
         <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G24" s="2">
         <v>45365</v>
@@ -2490,7 +2506,7 @@
         <v>-88.97</v>
       </c>
     </row>
-    <row r="25" spans="1:26">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>107</v>
       </c>
@@ -2507,7 +2523,7 @@
         <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G25" s="2">
         <v>45392</v>
@@ -2570,7 +2586,7 @@
         <v>14.8</v>
       </c>
     </row>
-    <row r="26" spans="1:26">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>108</v>
       </c>
@@ -2587,7 +2603,7 @@
         <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G26" s="2">
         <v>45392</v>
@@ -2652,5 +2668,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 Revvity Proprietary Information</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a1b582e8-0077-416f-9765-e019f2ce0792}" enabled="1" method="Standard" siteId="{66a92d0f-8ca8-403c-84e6-5503c5643994}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>